--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95436316</v>
+        <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>99103</v>
+        <v>87401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219799</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Syd Austers, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715103</v>
+        <v>715448</v>
       </c>
       <c r="R2" t="n">
-        <v>6411598</v>
+        <v>6411774</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,65 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95436316</t>
+          <t>https://artportalen.se/Sighting/137229354</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106585700</v>
+        <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>99120</v>
+        <v>87401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715215</v>
+        <v>715431</v>
       </c>
       <c r="R3" t="n">
-        <v>6411696</v>
+        <v>6411383</v>
       </c>
       <c r="S3" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,83 +884,64 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kärräng, tuvig, dikad.</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585700</t>
+          <t>https://artportalen.se/Sighting/137237008</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106585651</v>
+        <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>99156</v>
+        <v>87611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219875</v>
+        <v>433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Austers 1,95 km S (något till V), Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715218</v>
+        <v>715408</v>
       </c>
       <c r="R4" t="n">
-        <v>6411496</v>
+        <v>6411662</v>
       </c>
       <c r="S4" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,12 +965,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,45 +992,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>gräsmark, tunn jord</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585651</t>
+          <t>https://artportalen.se/Sighting/137240108</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106585693</v>
+        <v>137237009</v>
       </c>
       <c r="B5" t="n">
-        <v>106140</v>
+        <v>90854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +1023,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221137</v>
+        <v>970</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715215</v>
+        <v>715434</v>
       </c>
       <c r="R5" t="n">
-        <v>6411696</v>
+        <v>6411388</v>
       </c>
       <c r="S5" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,12 +1077,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,45 +1104,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kärräng, tuvig, dikad.</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585693</t>
+          <t>https://artportalen.se/Sighting/137237009</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95436433</v>
+        <v>137237013</v>
       </c>
       <c r="B6" t="n">
-        <v>107061</v>
+        <v>90854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,37 +1135,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221903</v>
+        <v>970</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Syd Austers, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715670</v>
+        <v>715446</v>
       </c>
       <c r="R6" t="n">
-        <v>6411322</v>
+        <v>6411339</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,12 +1189,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,65 +1219,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95436433</t>
+          <t>https://artportalen.se/Sighting/137237013</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106585699</v>
+        <v>137237024</v>
       </c>
       <c r="B7" t="n">
-        <v>99145</v>
+        <v>90854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222118</v>
+        <v>970</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715215</v>
+        <v>715408</v>
       </c>
       <c r="R7" t="n">
-        <v>6411696</v>
+        <v>6411311</v>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,12 +1301,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,45 +1328,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kärräng, tuvig, dikad.</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585699</t>
+          <t>https://artportalen.se/Sighting/137237024</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95436448</v>
+        <v>137237037</v>
       </c>
       <c r="B8" t="n">
-        <v>99803</v>
+        <v>90854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,37 +1359,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222322</v>
+        <v>970</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Syd Austers, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715252</v>
+        <v>715364</v>
       </c>
       <c r="R8" t="n">
-        <v>6411800</v>
+        <v>6411278</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,12 +1413,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,27 +1443,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95436448</t>
+          <t>https://artportalen.se/Sighting/137237037</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106585690</v>
+        <v>137239976</v>
       </c>
       <c r="B9" t="n">
-        <v>99803</v>
+        <v>90854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,37 +1471,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222322</v>
+        <v>970</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Hangvar bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715215</v>
+        <v>715429</v>
       </c>
       <c r="R9" t="n">
-        <v>6411696</v>
+        <v>6411387</v>
       </c>
       <c r="S9" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,12 +1525,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,45 +1552,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kärräng, tuvig, dikad.</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585690</t>
+          <t>https://artportalen.se/Sighting/137239976</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95436220</v>
+        <v>137240854</v>
       </c>
       <c r="B10" t="n">
-        <v>99879</v>
+        <v>90854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,37 +1583,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222361</v>
+        <v>970</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Syd Austers, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715088</v>
+        <v>715447</v>
       </c>
       <c r="R10" t="n">
-        <v>6411563</v>
+        <v>6411337</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,12 +1637,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tall, en, alvar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,65 +1672,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95436220</t>
+          <t>https://artportalen.se/Sighting/137240854</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106585703</v>
+        <v>137240113</v>
       </c>
       <c r="B11" t="n">
-        <v>99028</v>
+        <v>87530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223572</v>
+        <v>1988</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715215</v>
+        <v>715331</v>
       </c>
       <c r="R11" t="n">
-        <v>6411696</v>
+        <v>6411784</v>
       </c>
       <c r="S11" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,12 +1754,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,36 +1781,7558 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kärräng, tuvig, dikad.</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240113</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137240857</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91924</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>715455</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6411307</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>En, tall, alvar</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240857</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137237036</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Narrspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius pseudoarcuatorum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>715262</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6411321</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237036</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137229361</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>715318</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6411574</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137229361</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137237006</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>715432</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6411430</v>
+      </c>
+      <c r="S15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237006</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137237012</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>715438</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6411338</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237012</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137237032</v>
+      </c>
+      <c r="B17" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>715223</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6411376</v>
+      </c>
+      <c r="S17" t="n">
+        <v>16</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237032</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137237033</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>715219</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6411360</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237033</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137239979</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hangvar bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>715404</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6411241</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239979</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137240118</v>
+      </c>
+      <c r="B20" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>715325</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6411389</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240118</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137237023</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>715434</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6411225</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237023</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137240861</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>715531</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6411287</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gran, en, tall, alvar</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240861</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137229349</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87354</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>715573</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6411536</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137229349</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137240114</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87354</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>715328</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6411800</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240114</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137237016</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91537</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>715499</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6411302</v>
+      </c>
+      <c r="S25" t="n">
+        <v>12</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237016</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137240110</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91537</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>715397</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6411696</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240110</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137237014</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91597</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5735</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svartnande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phaeoclavulina macrospora</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Brinkmann</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>715451</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6411338</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237014</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137237038</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91597</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5735</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svartnande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phaeoclavulina macrospora</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Brinkmann</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>715404</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6411309</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237038</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137239978</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91597</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5735</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svartnande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phaeoclavulina macrospora</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Brinkmann</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hangvar bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>715449</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6411336</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239978</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137240864</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91597</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5735</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svartnande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phaeoclavulina macrospora</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Brinkmann</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>715406</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6411306</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>En, alvar</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240864</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>95436316</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99103</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Syd Austers, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>715103</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6411598</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-07-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95436316</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>106585700</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>715215</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6411696</v>
+      </c>
+      <c r="S32" t="n">
+        <v>71</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>Thomas Karlsson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
+      <c r="AY32" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585700</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>106585651</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Austers 1,95 km S (något till V), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>715218</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6411496</v>
+      </c>
+      <c r="S33" t="n">
+        <v>71</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>gräsmark, tunn jord</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585651</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137237031</v>
+      </c>
+      <c r="B34" t="n">
+        <v>104924</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>715277</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6411394</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237031</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>106585693</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>715215</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6411696</v>
+      </c>
+      <c r="S35" t="n">
+        <v>71</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585693</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137237019</v>
+      </c>
+      <c r="B36" t="n">
+        <v>107807</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>715513</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6411248</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237019</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137240107</v>
+      </c>
+      <c r="B37" t="n">
+        <v>107807</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>715423</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6411609</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240107</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>95436433</v>
+      </c>
+      <c r="B38" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Syd Austers, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>715670</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6411322</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2021-07-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95436433</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>106585699</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99145</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>715215</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6411696</v>
+      </c>
+      <c r="S39" t="n">
+        <v>71</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585699</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>95436448</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Syd Austers, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>715252</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6411800</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2021-07-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95436448</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>106585690</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>715215</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6411696</v>
+      </c>
+      <c r="S41" t="n">
+        <v>71</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106585690</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>95436220</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99879</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222361</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Loppstarr</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carex pulicaris</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Syd Austers, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>715088</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6411563</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2021-07-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2021-08-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95436220</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>106585703</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99028</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>715215</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6411696</v>
+      </c>
+      <c r="S43" t="n">
+        <v>71</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1996-06-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/106585703</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137237021</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90880</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>715471</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6411240</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237021</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137229353</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>715413</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6411769</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137229353</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137237015</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>715496</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6411333</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237015</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137237017</v>
+      </c>
+      <c r="B47" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>715516</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6411294</v>
+      </c>
+      <c r="S47" t="n">
+        <v>7</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237017</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137237029</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>715284</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6411357</v>
+      </c>
+      <c r="S48" t="n">
+        <v>7</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237029</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137239982</v>
+      </c>
+      <c r="B49" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hangvar bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>715286</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6411356</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239982</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137240117</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>715319</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6411401</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240117</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137229352</v>
+      </c>
+      <c r="B51" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>715400</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6411777</v>
+      </c>
+      <c r="S51" t="n">
+        <v>8</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137229352</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137237011</v>
+      </c>
+      <c r="B52" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>715428</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6411352</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237011</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137237020</v>
+      </c>
+      <c r="B53" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>715504</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6411243</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237020</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137237026</v>
+      </c>
+      <c r="B54" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>715319</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6411360</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137237030</v>
+      </c>
+      <c r="B55" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>715298</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6411357</v>
+      </c>
+      <c r="S55" t="n">
+        <v>7</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237030</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137239975</v>
+      </c>
+      <c r="B56" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hangvar bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>715471</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6411433</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239975</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137240109</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>715411</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6411662</v>
+      </c>
+      <c r="S57" t="n">
+        <v>8</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240109</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137240112</v>
+      </c>
+      <c r="B58" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>715357</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6411791</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240112</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137240115</v>
+      </c>
+      <c r="B59" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>715346</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6411701</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240115</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>137240119</v>
+      </c>
+      <c r="B60" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>715328</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6411384</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240119</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>137240860</v>
+      </c>
+      <c r="B61" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>715534</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6411281</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Tall, en, alvar</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240860</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>137229356</v>
+      </c>
+      <c r="B62" t="n">
+        <v>87306</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>715420</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6411796</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137229356</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>137229350</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90922</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>249376</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ullmusseron</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tricholoma squarrulosum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bres.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>715463</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6411631</v>
+      </c>
+      <c r="S63" t="n">
+        <v>9</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137229350</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>137229355</v>
+      </c>
+      <c r="B64" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>715420</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6411796</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137229355</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>137237004</v>
+      </c>
+      <c r="B65" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>715571</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6411459</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237004</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137237007</v>
+      </c>
+      <c r="B66" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>715435</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6411420</v>
+      </c>
+      <c r="S66" t="n">
+        <v>16</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237007</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>137237010</v>
+      </c>
+      <c r="B67" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>715416</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6411386</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237010</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>137237025</v>
+      </c>
+      <c r="B68" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>715360</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6411366</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237025</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>137237028</v>
+      </c>
+      <c r="B69" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>715269</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6411339</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237028</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>137239981</v>
+      </c>
+      <c r="B70" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hangvar bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>715326</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6411358</v>
+      </c>
+      <c r="S70" t="n">
+        <v>6</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137239981</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>137240111</v>
+      </c>
+      <c r="B71" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>715350</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6411745</v>
+      </c>
+      <c r="S71" t="n">
+        <v>8</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240111</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>137240868</v>
+      </c>
+      <c r="B72" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>715283</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6411355</v>
+      </c>
+      <c r="S72" t="n">
+        <v>9</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>En, tall</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240868</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>137240869</v>
+      </c>
+      <c r="B73" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>715275</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6411419</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>En, tall, mossa, gräs</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240869</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>137240870</v>
+      </c>
+      <c r="B74" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>715579</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6411450</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240870</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>137240862</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91532</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6003554</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Sträv jordstjärna</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Geastrum berkeleyi</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Massee</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>715487</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6411240</v>
+      </c>
+      <c r="S75" t="n">
+        <v>7</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Brakved, en, tall</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240862</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>137237018</v>
+      </c>
+      <c r="B76" t="n">
+        <v>87520</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>715520</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6411260</v>
+      </c>
+      <c r="S76" t="n">
+        <v>11</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237018</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>137240116</v>
+      </c>
+      <c r="B77" t="n">
+        <v>87520</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>715273</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6411613</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240116</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>137237022</v>
+      </c>
+      <c r="B78" t="n">
+        <v>90824</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6049769</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Clitopaxillus alexandri</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Gillet) G.Moreno &amp; al.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>715442</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6411226</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237022</t>
         </is>
       </c>
     </row>
@@ -1800,6 +9348,73 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137237009</v>
       </c>
       <c r="B5" t="n">
-        <v>90854</v>
+        <v>90856</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137237013</v>
       </c>
       <c r="B6" t="n">
-        <v>90854</v>
+        <v>90856</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137237024</v>
       </c>
       <c r="B7" t="n">
-        <v>90854</v>
+        <v>90856</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137237037</v>
       </c>
       <c r="B8" t="n">
-        <v>90854</v>
+        <v>90856</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137239976</v>
       </c>
       <c r="B9" t="n">
-        <v>90854</v>
+        <v>90856</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137240854</v>
       </c>
       <c r="B10" t="n">
-        <v>90854</v>
+        <v>90856</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137240113</v>
       </c>
       <c r="B11" t="n">
-        <v>87530</v>
+        <v>87532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137240857</v>
       </c>
       <c r="B12" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>137237036</v>
       </c>
       <c r="B13" t="n">
-        <v>87541</v>
+        <v>87543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137229361</v>
       </c>
       <c r="B14" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137237006</v>
       </c>
       <c r="B15" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>137237012</v>
       </c>
       <c r="B16" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137237032</v>
       </c>
       <c r="B17" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137237033</v>
       </c>
       <c r="B18" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137239979</v>
       </c>
       <c r="B19" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>137240118</v>
       </c>
       <c r="B20" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137237023</v>
       </c>
       <c r="B21" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>137240861</v>
       </c>
       <c r="B22" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>137229349</v>
       </c>
       <c r="B23" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>137240114</v>
       </c>
       <c r="B24" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>137237016</v>
       </c>
       <c r="B25" t="n">
-        <v>91537</v>
+        <v>91539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>137240110</v>
       </c>
       <c r="B26" t="n">
-        <v>91537</v>
+        <v>91539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>137237014</v>
       </c>
       <c r="B27" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>137237038</v>
       </c>
       <c r="B28" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>137239978</v>
       </c>
       <c r="B29" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>137240864</v>
       </c>
       <c r="B30" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>137237031</v>
       </c>
       <c r="B34" t="n">
-        <v>104924</v>
+        <v>104926</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>137237019</v>
       </c>
       <c r="B36" t="n">
-        <v>107807</v>
+        <v>107809</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>137240107</v>
       </c>
       <c r="B37" t="n">
-        <v>107807</v>
+        <v>107809</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>137237021</v>
       </c>
       <c r="B44" t="n">
-        <v>90880</v>
+        <v>90882</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137229353</v>
       </c>
       <c r="B45" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>137237015</v>
       </c>
       <c r="B46" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>137237017</v>
       </c>
       <c r="B47" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>137237029</v>
       </c>
       <c r="B48" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>137239982</v>
       </c>
       <c r="B49" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>137240117</v>
       </c>
       <c r="B50" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>137229352</v>
       </c>
       <c r="B51" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>137237011</v>
       </c>
       <c r="B52" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>137237020</v>
       </c>
       <c r="B53" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>137237026</v>
       </c>
       <c r="B54" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>137237030</v>
       </c>
       <c r="B55" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>137239975</v>
       </c>
       <c r="B56" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>137240109</v>
       </c>
       <c r="B57" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>137240112</v>
       </c>
       <c r="B58" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>137240115</v>
       </c>
       <c r="B59" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>137240119</v>
       </c>
       <c r="B60" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>137240860</v>
       </c>
       <c r="B61" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>137229356</v>
       </c>
       <c r="B62" t="n">
-        <v>87306</v>
+        <v>87308</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>137229350</v>
       </c>
       <c r="B63" t="n">
-        <v>90922</v>
+        <v>90924</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>137229355</v>
       </c>
       <c r="B64" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>137237004</v>
       </c>
       <c r="B65" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>137237007</v>
       </c>
       <c r="B66" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>137237010</v>
       </c>
       <c r="B67" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>137237025</v>
       </c>
       <c r="B68" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>137237028</v>
       </c>
       <c r="B69" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>137239981</v>
       </c>
       <c r="B70" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>137240111</v>
       </c>
       <c r="B71" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>137240868</v>
       </c>
       <c r="B72" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>137240869</v>
       </c>
       <c r="B73" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>137240870</v>
       </c>
       <c r="B74" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>137240862</v>
       </c>
       <c r="B75" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>137237018</v>
       </c>
       <c r="B76" t="n">
-        <v>87520</v>
+        <v>87522</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>137240116</v>
       </c>
       <c r="B77" t="n">
-        <v>87520</v>
+        <v>87522</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>137237022</v>
       </c>
       <c r="B78" t="n">
-        <v>90824</v>
+        <v>90826</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ78"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,34 +1012,30 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137237009</v>
+        <v>137274059</v>
       </c>
       <c r="B5" t="n">
-        <v>90856</v>
+        <v>87616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>970</v>
+        <v>433</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Quél.) Kotl.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1047,13 +1043,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715434</v>
+        <v>715263</v>
       </c>
       <c r="R5" t="n">
-        <v>6411388</v>
+        <v>6411474</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,24 +1103,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237009</t>
+          <t>https://artportalen.se/Sighting/137274059</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137237013</v>
+        <v>137237009</v>
       </c>
       <c r="B6" t="n">
         <v>90856</v>
@@ -1159,13 +1155,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715446</v>
+        <v>715434</v>
       </c>
       <c r="R6" t="n">
-        <v>6411339</v>
+        <v>6411388</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1190,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,7 +1200,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,13 +1226,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237013</t>
+          <t>https://artportalen.se/Sighting/137237009</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137237024</v>
+        <v>137237013</v>
       </c>
       <c r="B7" t="n">
         <v>90856</v>
@@ -1271,13 +1267,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715408</v>
+        <v>715446</v>
       </c>
       <c r="R7" t="n">
-        <v>6411311</v>
+        <v>6411339</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,13 +1338,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237024</t>
+          <t>https://artportalen.se/Sighting/137237013</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137237037</v>
+        <v>137237024</v>
       </c>
       <c r="B8" t="n">
         <v>90856</v>
@@ -1383,13 +1379,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715364</v>
+        <v>715408</v>
       </c>
       <c r="R8" t="n">
-        <v>6411278</v>
+        <v>6411311</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,13 +1450,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237037</t>
+          <t>https://artportalen.se/Sighting/137237024</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137239976</v>
+        <v>137237037</v>
       </c>
       <c r="B9" t="n">
         <v>90856</v>
@@ -1491,17 +1487,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hangvar bäcks, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715429</v>
+        <v>715364</v>
       </c>
       <c r="R9" t="n">
-        <v>6411387</v>
+        <v>6411278</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,24 +1551,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239976</t>
+          <t>https://artportalen.se/Sighting/137237037</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137240854</v>
+        <v>137239976</v>
       </c>
       <c r="B10" t="n">
         <v>90856</v>
@@ -1603,17 +1599,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hangvar Bäcks, Gtl</t>
+          <t>Hangvar bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715447</v>
+        <v>715429</v>
       </c>
       <c r="R10" t="n">
-        <v>6411337</v>
+        <v>6411387</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,12 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tall, en, alvar</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,27 +1663,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240854</t>
+          <t>https://artportalen.se/Sighting/137239976</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137240113</v>
+        <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>87532</v>
+        <v>90856</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,21 +1691,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1988</v>
+        <v>970</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1724,13 +1715,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715331</v>
+        <v>715447</v>
       </c>
       <c r="R11" t="n">
-        <v>6411784</v>
+        <v>6411337</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,7 +1750,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1760,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tall, en, alvar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,49 +1780,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240113</t>
+          <t>https://artportalen.se/Sighting/137240854</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137240857</v>
+        <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>91926</v>
+        <v>87532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2015</v>
+        <v>1988</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1836,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715455</v>
+        <v>715331</v>
       </c>
       <c r="R12" t="n">
-        <v>6411307</v>
+        <v>6411784</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1871,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1881,12 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En, tall, alvar</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,27 +1892,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240857</t>
+          <t>https://artportalen.se/Sighting/137240113</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137237036</v>
+        <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>87543</v>
+        <v>91926</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,21 +1920,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3599</v>
+        <v>2015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Rob.Henry</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1953,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715262</v>
+        <v>715455</v>
       </c>
       <c r="R13" t="n">
-        <v>6411321</v>
+        <v>6411307</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1988,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1998,7 +1989,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En, tall, alvar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,49 +2009,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237036</t>
+          <t>https://artportalen.se/Sighting/137240857</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137229361</v>
+        <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87519</v>
+        <v>87543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3674</v>
+        <v>3599</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2065,13 +2061,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715318</v>
+        <v>715262</v>
       </c>
       <c r="R14" t="n">
-        <v>6411574</v>
+        <v>6411321</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2100,7 +2096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2110,7 +2106,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,24 +2121,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137229361</t>
+          <t>https://artportalen.se/Sighting/137237036</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137237006</v>
+        <v>137229361</v>
       </c>
       <c r="B15" t="n">
         <v>87519</v>
@@ -2177,13 +2173,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715432</v>
+        <v>715318</v>
       </c>
       <c r="R15" t="n">
-        <v>6411430</v>
+        <v>6411574</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2212,7 +2208,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2218,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,24 +2233,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237006</t>
+          <t>https://artportalen.se/Sighting/137229361</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137237012</v>
+        <v>137237006</v>
       </c>
       <c r="B16" t="n">
         <v>87519</v>
@@ -2289,13 +2285,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715438</v>
+        <v>715432</v>
       </c>
       <c r="R16" t="n">
-        <v>6411338</v>
+        <v>6411430</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,7 +2320,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,7 +2330,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,13 +2356,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237012</t>
+          <t>https://artportalen.se/Sighting/137237006</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137237032</v>
+        <v>137237012</v>
       </c>
       <c r="B17" t="n">
         <v>87519</v>
@@ -2401,13 +2397,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715223</v>
+        <v>715438</v>
       </c>
       <c r="R17" t="n">
-        <v>6411376</v>
+        <v>6411338</v>
       </c>
       <c r="S17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,7 +2432,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,7 +2442,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,13 +2468,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237032</t>
+          <t>https://artportalen.se/Sighting/137237012</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137237033</v>
+        <v>137237032</v>
       </c>
       <c r="B18" t="n">
         <v>87519</v>
@@ -2513,13 +2509,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715219</v>
+        <v>715223</v>
       </c>
       <c r="R18" t="n">
-        <v>6411360</v>
+        <v>6411376</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,7 +2544,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2558,7 +2554,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,13 +2580,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237033</t>
+          <t>https://artportalen.se/Sighting/137237032</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137239979</v>
+        <v>137237033</v>
       </c>
       <c r="B19" t="n">
         <v>87519</v>
@@ -2621,17 +2617,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hangvar bäcks, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715404</v>
+        <v>715219</v>
       </c>
       <c r="R19" t="n">
-        <v>6411241</v>
+        <v>6411360</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,7 +2656,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2670,7 +2666,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,24 +2681,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239979</t>
+          <t>https://artportalen.se/Sighting/137237033</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137240118</v>
+        <v>137239979</v>
       </c>
       <c r="B20" t="n">
         <v>87519</v>
@@ -2733,17 +2729,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hangvar Bäcks, Gtl</t>
+          <t>Hangvar bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715325</v>
+        <v>715404</v>
       </c>
       <c r="R20" t="n">
-        <v>6411389</v>
+        <v>6411241</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,7 +2768,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2782,7 +2778,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2797,49 +2793,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240118</t>
+          <t>https://artportalen.se/Sighting/137239979</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137237023</v>
+        <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87380</v>
+        <v>87519</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,13 +2845,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715434</v>
+        <v>715325</v>
       </c>
       <c r="R21" t="n">
-        <v>6411225</v>
+        <v>6411389</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2884,7 +2880,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2890,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2909,49 +2905,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237023</t>
+          <t>https://artportalen.se/Sighting/137240118</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137240861</v>
+        <v>137274058</v>
       </c>
       <c r="B22" t="n">
-        <v>87380</v>
+        <v>87522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2961,10 +2957,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715531</v>
+        <v>715276</v>
       </c>
       <c r="R22" t="n">
-        <v>6411287</v>
+        <v>6411487</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2996,7 +2992,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,12 +3002,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran, en, tall, alvar</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,49 +3017,49 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240861</t>
+          <t>https://artportalen.se/Sighting/137274058</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137229349</v>
+        <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87356</v>
+        <v>87380</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3078,13 +3069,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715573</v>
+        <v>715434</v>
       </c>
       <c r="R23" t="n">
-        <v>6411536</v>
+        <v>6411225</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,7 +3104,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3114,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3138,49 +3129,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137229349</t>
+          <t>https://artportalen.se/Sighting/137237023</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137240114</v>
+        <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87356</v>
+        <v>87380</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3181,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>715328</v>
+        <v>715531</v>
       </c>
       <c r="R24" t="n">
-        <v>6411800</v>
+        <v>6411287</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3225,7 +3216,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3226,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gran, en, tall, alvar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3250,27 +3246,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240114</t>
+          <t>https://artportalen.se/Sighting/137240861</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137237016</v>
+        <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>91539</v>
+        <v>87356</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,21 +3274,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4188</v>
+        <v>3762</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,13 +3298,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715499</v>
+        <v>715573</v>
       </c>
       <c r="R25" t="n">
-        <v>6411302</v>
+        <v>6411536</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3337,7 +3333,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3343,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,27 +3358,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237016</t>
+          <t>https://artportalen.se/Sighting/137229349</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137240110</v>
+        <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>91539</v>
+        <v>87356</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,21 +3386,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4188</v>
+        <v>3762</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3414,13 +3410,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715397</v>
+        <v>715328</v>
       </c>
       <c r="R26" t="n">
-        <v>6411696</v>
+        <v>6411800</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3449,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,38 +3481,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240110</t>
+          <t>https://artportalen.se/Sighting/137240114</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137237014</v>
+        <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91599</v>
+        <v>91539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5735</v>
+        <v>4188</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3526,13 +3522,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715451</v>
+        <v>715499</v>
       </c>
       <c r="R27" t="n">
-        <v>6411338</v>
+        <v>6411302</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3561,7 +3557,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3567,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,38 +3593,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237014</t>
+          <t>https://artportalen.se/Sighting/137237016</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137237038</v>
+        <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>91539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5735</v>
+        <v>4188</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartnande fingersvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phaeoclavulina macrospora</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brinkmann</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3638,13 +3634,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715404</v>
+        <v>715397</v>
       </c>
       <c r="R28" t="n">
-        <v>6411309</v>
+        <v>6411696</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3673,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,24 +3694,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237038</t>
+          <t>https://artportalen.se/Sighting/137240110</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137239978</v>
+        <v>137237014</v>
       </c>
       <c r="B29" t="n">
         <v>91599</v>
@@ -3746,17 +3742,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hangvar bäcks, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715449</v>
+        <v>715451</v>
       </c>
       <c r="R29" t="n">
-        <v>6411336</v>
+        <v>6411338</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3785,7 +3781,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3791,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,24 +3806,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239978</t>
+          <t>https://artportalen.se/Sighting/137237014</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137240864</v>
+        <v>137237038</v>
       </c>
       <c r="B30" t="n">
         <v>91599</v>
@@ -3862,13 +3858,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715406</v>
+        <v>715404</v>
       </c>
       <c r="R30" t="n">
-        <v>6411306</v>
+        <v>6411309</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3897,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,12 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>En, alvar</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3927,65 +3918,65 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240864</t>
+          <t>https://artportalen.se/Sighting/137237038</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>95436316</v>
+        <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>99103</v>
+        <v>91599</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219799</v>
+        <v>5735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Syd Austers, Gtl</t>
+          <t>Hangvar bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715103</v>
+        <v>715449</v>
       </c>
       <c r="R31" t="n">
-        <v>6411598</v>
+        <v>6411336</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4009,12 +4000,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4029,65 +4030,65 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95436316</t>
+          <t>https://artportalen.se/Sighting/137239978</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>106585700</v>
+        <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>99120</v>
+        <v>91599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219811</v>
+        <v>5735</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Svartnande fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Phaeoclavulina macrospora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Brinkmann</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715215</v>
+        <v>715406</v>
       </c>
       <c r="R32" t="n">
-        <v>6411696</v>
+        <v>6411306</v>
       </c>
       <c r="S32" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4111,12 +4112,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>En, alvar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4128,45 +4144,30 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Kärräng, tuvig, dikad.</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr"/>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585700</t>
+          <t>https://artportalen.se/Sighting/137240864</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>106585651</v>
+        <v>95436316</v>
       </c>
       <c r="B33" t="n">
-        <v>99156</v>
+        <v>99103</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4174,37 +4175,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219875</v>
+        <v>219799</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Austers 1,95 km S (något till V), Gtl</t>
+          <t>Syd Austers, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715218</v>
+        <v>715103</v>
       </c>
       <c r="R33" t="n">
-        <v>6411496</v>
+        <v>6411598</v>
       </c>
       <c r="S33" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4228,12 +4229,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4245,83 +4246,68 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>gräsmark, tunn jord</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr"/>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585651</t>
+          <t>https://artportalen.se/Sighting/95436316</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137237031</v>
+        <v>106585700</v>
       </c>
       <c r="B34" t="n">
-        <v>104926</v>
+        <v>99120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220164</v>
+        <v>219811</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hangvar Bäcks, Gtl</t>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715277</v>
+        <v>715215</v>
       </c>
       <c r="R34" t="n">
-        <v>6411394</v>
+        <v>6411696</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4345,22 +4331,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>1996-06-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>1996-06-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4372,65 +4348,80 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr"/>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237031</t>
+          <t>https://artportalen.se/Sighting/106585700</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>106585693</v>
+        <v>106585651</v>
       </c>
       <c r="B35" t="n">
-        <v>106140</v>
+        <v>99156</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221137</v>
+        <v>219875</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Austers 1,95 km S (något till V), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715215</v>
+        <v>715218</v>
       </c>
       <c r="R35" t="n">
-        <v>6411696</v>
+        <v>6411496</v>
       </c>
       <c r="S35" t="n">
         <v>71</v>
@@ -4476,7 +4467,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Kärräng, tuvig, dikad.</t>
+          <t>gräsmark, tunn jord</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
@@ -4503,16 +4494,16 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585693</t>
+          <t>https://artportalen.se/Sighting/106585651</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137237019</v>
+        <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>107809</v>
+        <v>104926</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4520,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4544,10 +4535,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715513</v>
+        <v>715277</v>
       </c>
       <c r="R36" t="n">
-        <v>6411248</v>
+        <v>6411394</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4579,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4589,7 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4615,16 +4606,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237019</t>
+          <t>https://artportalen.se/Sighting/137237031</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137240107</v>
+        <v>106585693</v>
       </c>
       <c r="B37" t="n">
-        <v>107809</v>
+        <v>106140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4632,16 +4623,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>221137</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4652,17 +4643,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hangvar Bäcks, Gtl</t>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715423</v>
+        <v>715215</v>
       </c>
       <c r="R37" t="n">
-        <v>6411609</v>
+        <v>6411696</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4686,22 +4677,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:29</t>
+          <t>1996-06-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:29</t>
+          <t>1996-06-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4713,30 +4694,45 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr"/>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240107</t>
+          <t>https://artportalen.se/Sighting/106585693</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>95436433</v>
+        <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107061</v>
+        <v>107809</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4744,16 +4740,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4764,17 +4760,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Syd Austers, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715670</v>
+        <v>715513</v>
       </c>
       <c r="R38" t="n">
-        <v>6411322</v>
+        <v>6411248</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4798,12 +4794,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4818,44 +4824,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95436433</t>
+          <t>https://artportalen.se/Sighting/137237019</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>106585699</v>
+        <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>99145</v>
+        <v>107809</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222118</v>
+        <v>221849</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Flugblomster</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ophrys insectifera</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4866,17 +4872,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Austers 1,7 km S (något till V), Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715215</v>
+        <v>715423</v>
       </c>
       <c r="R39" t="n">
-        <v>6411696</v>
+        <v>6411609</v>
       </c>
       <c r="S39" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4900,12 +4906,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1996-06-30</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4917,45 +4933,30 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Kärräng, tuvig, dikad.</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585699</t>
+          <t>https://artportalen.se/Sighting/137240107</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>95436448</v>
+        <v>95436433</v>
       </c>
       <c r="B40" t="n">
-        <v>99803</v>
+        <v>107061</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4963,21 +4964,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222322</v>
+        <v>221903</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4987,10 +4988,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715252</v>
+        <v>715670</v>
       </c>
       <c r="R40" t="n">
-        <v>6411800</v>
+        <v>6411322</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5048,38 +5049,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95436448</t>
+          <t>https://artportalen.se/Sighting/95436433</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>106585690</v>
+        <v>106585699</v>
       </c>
       <c r="B41" t="n">
-        <v>99803</v>
+        <v>99145</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222322</v>
+        <v>222118</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Flugblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Ophrys insectifera</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,16 +5166,16 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585690</t>
+          <t>https://artportalen.se/Sighting/106585699</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>95436220</v>
+        <v>95436448</v>
       </c>
       <c r="B42" t="n">
-        <v>99879</v>
+        <v>99803</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5182,21 +5183,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222361</v>
+        <v>222322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5206,10 +5207,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715088</v>
+        <v>715252</v>
       </c>
       <c r="R42" t="n">
-        <v>6411563</v>
+        <v>6411800</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5267,38 +5268,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95436220</t>
+          <t>https://artportalen.se/Sighting/95436448</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>106585703</v>
+        <v>106585690</v>
       </c>
       <c r="B43" t="n">
-        <v>99028</v>
+        <v>99803</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>223572</v>
+        <v>222322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5384,54 +5385,54 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106585703</t>
+          <t>https://artportalen.se/Sighting/106585690</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137237021</v>
+        <v>95436220</v>
       </c>
       <c r="B44" t="n">
-        <v>90882</v>
+        <v>99879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>245042</v>
+        <v>222361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hangvar Bäcks, Gtl</t>
+          <t>Syd Austers, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715471</v>
+        <v>715088</v>
       </c>
       <c r="R44" t="n">
-        <v>6411240</v>
+        <v>6411563</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5455,22 +5456,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5479,72 +5470,71 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237021</t>
+          <t>https://artportalen.se/Sighting/95436220</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137229353</v>
+        <v>106585703</v>
       </c>
       <c r="B45" t="n">
-        <v>87579</v>
+        <v>99028</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>248947</v>
+        <v>223572</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hangvar Bäcks, Gtl</t>
+          <t>Austers 1,7 km S (något till V), Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715413</v>
+        <v>715215</v>
       </c>
       <c r="R45" t="n">
-        <v>6411769</v>
+        <v>6411696</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5568,22 +5558,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>1996-06-30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>1996-06-30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5595,52 +5575,67 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kärräng, tuvig, dikad.</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr"/>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137229353</t>
+          <t>https://artportalen.se/Sighting/106585703</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137237015</v>
+        <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>87579</v>
+        <v>90882</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>248947</v>
+        <v>245042</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5650,10 +5645,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715496</v>
+        <v>715471</v>
       </c>
       <c r="R46" t="n">
-        <v>6411333</v>
+        <v>6411240</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5685,7 +5680,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5695,7 +5690,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5704,6 +5699,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5721,13 +5717,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237015</t>
+          <t>https://artportalen.se/Sighting/137237021</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137237017</v>
+        <v>137229353</v>
       </c>
       <c r="B47" t="n">
         <v>87579</v>
@@ -5762,13 +5758,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715516</v>
+        <v>715413</v>
       </c>
       <c r="R47" t="n">
-        <v>6411294</v>
+        <v>6411769</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5797,7 +5793,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5807,7 +5803,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5822,24 +5818,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237017</t>
+          <t>https://artportalen.se/Sighting/137229353</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137237029</v>
+        <v>137237015</v>
       </c>
       <c r="B48" t="n">
         <v>87579</v>
@@ -5874,13 +5870,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715284</v>
+        <v>715496</v>
       </c>
       <c r="R48" t="n">
-        <v>6411357</v>
+        <v>6411333</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5909,7 +5905,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5919,7 +5915,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5945,13 +5941,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237029</t>
+          <t>https://artportalen.se/Sighting/137237015</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137239982</v>
+        <v>137237017</v>
       </c>
       <c r="B49" t="n">
         <v>87579</v>
@@ -5982,17 +5978,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hangvar bäcks, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715286</v>
+        <v>715516</v>
       </c>
       <c r="R49" t="n">
-        <v>6411356</v>
+        <v>6411294</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6021,7 +6017,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6031,7 +6027,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6046,24 +6042,24 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239982</t>
+          <t>https://artportalen.se/Sighting/137237017</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137240117</v>
+        <v>137237029</v>
       </c>
       <c r="B50" t="n">
         <v>87579</v>
@@ -6098,13 +6094,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>715319</v>
+        <v>715284</v>
       </c>
       <c r="R50" t="n">
-        <v>6411401</v>
+        <v>6411357</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6133,7 +6129,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6143,7 +6139,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6158,27 +6154,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240117</t>
+          <t>https://artportalen.se/Sighting/137237029</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137229352</v>
+        <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87472</v>
+        <v>87579</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6186,37 +6182,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hangvar Bäcks, Gtl</t>
+          <t>Hangvar bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715400</v>
+        <v>715286</v>
       </c>
       <c r="R51" t="n">
-        <v>6411777</v>
+        <v>6411356</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6245,7 +6241,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6255,7 +6251,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6270,27 +6266,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137229352</t>
+          <t>https://artportalen.se/Sighting/137239982</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137237011</v>
+        <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87472</v>
+        <v>87579</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6298,21 +6294,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6322,10 +6318,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715428</v>
+        <v>715319</v>
       </c>
       <c r="R52" t="n">
-        <v>6411352</v>
+        <v>6411401</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6357,7 +6353,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6367,7 +6363,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6376,31 +6372,30 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237011</t>
+          <t>https://artportalen.se/Sighting/137240117</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137237020</v>
+        <v>137229352</v>
       </c>
       <c r="B53" t="n">
         <v>87472</v>
@@ -6435,13 +6430,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715504</v>
+        <v>715400</v>
       </c>
       <c r="R53" t="n">
-        <v>6411243</v>
+        <v>6411777</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6470,7 +6465,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6480,7 +6475,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6495,24 +6490,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237020</t>
+          <t>https://artportalen.se/Sighting/137229352</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137237026</v>
+        <v>137237011</v>
       </c>
       <c r="B54" t="n">
         <v>87472</v>
@@ -6547,10 +6542,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715319</v>
+        <v>715428</v>
       </c>
       <c r="R54" t="n">
-        <v>6411360</v>
+        <v>6411352</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6582,7 +6577,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6592,7 +6587,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6601,6 +6596,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6618,13 +6614,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237026</t>
+          <t>https://artportalen.se/Sighting/137237011</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137237030</v>
+        <v>137237020</v>
       </c>
       <c r="B55" t="n">
         <v>87472</v>
@@ -6659,13 +6655,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715298</v>
+        <v>715504</v>
       </c>
       <c r="R55" t="n">
-        <v>6411357</v>
+        <v>6411243</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6694,7 +6690,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6704,7 +6700,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6730,13 +6726,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237030</t>
+          <t>https://artportalen.se/Sighting/137237020</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137239975</v>
+        <v>137237026</v>
       </c>
       <c r="B56" t="n">
         <v>87472</v>
@@ -6767,14 +6763,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hangvar bäcks, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715471</v>
+        <v>715319</v>
       </c>
       <c r="R56" t="n">
-        <v>6411433</v>
+        <v>6411360</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6806,7 +6802,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6816,7 +6812,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6831,24 +6827,24 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239975</t>
+          <t>https://artportalen.se/Sighting/137237026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137240109</v>
+        <v>137237030</v>
       </c>
       <c r="B57" t="n">
         <v>87472</v>
@@ -6883,13 +6879,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715411</v>
+        <v>715298</v>
       </c>
       <c r="R57" t="n">
-        <v>6411662</v>
+        <v>6411357</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6918,7 +6914,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6928,7 +6924,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6943,24 +6939,24 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240109</t>
+          <t>https://artportalen.se/Sighting/137237030</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137240112</v>
+        <v>137239975</v>
       </c>
       <c r="B58" t="n">
         <v>87472</v>
@@ -6991,14 +6987,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hangvar Bäcks, Gtl</t>
+          <t>Hangvar bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715357</v>
+        <v>715471</v>
       </c>
       <c r="R58" t="n">
-        <v>6411791</v>
+        <v>6411433</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7030,7 +7026,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7040,7 +7036,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7055,24 +7051,24 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240112</t>
+          <t>https://artportalen.se/Sighting/137239975</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137240115</v>
+        <v>137240109</v>
       </c>
       <c r="B59" t="n">
         <v>87472</v>
@@ -7107,13 +7103,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715346</v>
+        <v>715411</v>
       </c>
       <c r="R59" t="n">
-        <v>6411701</v>
+        <v>6411662</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7142,7 +7138,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7152,7 +7148,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7178,13 +7174,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240115</t>
+          <t>https://artportalen.se/Sighting/137240109</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137240119</v>
+        <v>137240112</v>
       </c>
       <c r="B60" t="n">
         <v>87472</v>
@@ -7219,10 +7215,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715328</v>
+        <v>715357</v>
       </c>
       <c r="R60" t="n">
-        <v>6411384</v>
+        <v>6411791</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7254,7 +7250,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7264,7 +7260,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7290,13 +7286,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240119</t>
+          <t>https://artportalen.se/Sighting/137240112</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137240860</v>
+        <v>137240115</v>
       </c>
       <c r="B61" t="n">
         <v>87472</v>
@@ -7331,10 +7327,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715534</v>
+        <v>715346</v>
       </c>
       <c r="R61" t="n">
-        <v>6411281</v>
+        <v>6411701</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7366,7 +7362,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7376,12 +7372,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Tall, en, alvar</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7396,49 +7387,49 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240860</t>
+          <t>https://artportalen.se/Sighting/137240115</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137229356</v>
+        <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87308</v>
+        <v>87472</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>249278</v>
+        <v>248956</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7448,10 +7439,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715420</v>
+        <v>715328</v>
       </c>
       <c r="R62" t="n">
-        <v>6411796</v>
+        <v>6411384</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7483,7 +7474,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7493,7 +7484,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7508,27 +7499,27 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137229356</t>
+          <t>https://artportalen.se/Sighting/137240119</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137229350</v>
+        <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>90924</v>
+        <v>87472</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7536,21 +7527,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>249376</v>
+        <v>248956</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullmusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tricholoma squarrulosum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bres.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7560,13 +7551,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715463</v>
+        <v>715534</v>
       </c>
       <c r="R63" t="n">
-        <v>6411631</v>
+        <v>6411281</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7595,7 +7586,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7605,7 +7596,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Tall, en, alvar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7620,49 +7616,49 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137229350</t>
+          <t>https://artportalen.se/Sighting/137240860</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137229355</v>
+        <v>137274060</v>
       </c>
       <c r="B64" t="n">
-        <v>87556</v>
+        <v>87475</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7672,10 +7668,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715420</v>
+        <v>715324</v>
       </c>
       <c r="R64" t="n">
-        <v>6411796</v>
+        <v>6411390</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7707,7 +7703,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7717,7 +7713,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7732,49 +7728,49 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137229355</t>
+          <t>https://artportalen.se/Sighting/137274060</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137237004</v>
+        <v>137274064</v>
       </c>
       <c r="B65" t="n">
-        <v>87556</v>
+        <v>87475</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7784,10 +7780,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>715571</v>
+        <v>715506</v>
       </c>
       <c r="R65" t="n">
-        <v>6411459</v>
+        <v>6411400</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7819,7 +7815,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7829,7 +7825,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7838,34 +7834,33 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237004</t>
+          <t>https://artportalen.se/Sighting/137274064</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137237007</v>
+        <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87556</v>
+        <v>87308</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7873,21 +7868,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6003295</v>
+        <v>249278</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7897,13 +7892,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715435</v>
+        <v>715420</v>
       </c>
       <c r="R66" t="n">
-        <v>6411420</v>
+        <v>6411796</v>
       </c>
       <c r="S66" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7932,7 +7927,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7942,7 +7937,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7951,56 +7946,55 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237007</t>
+          <t>https://artportalen.se/Sighting/137229356</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>137237010</v>
+        <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>87556</v>
+        <v>90924</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>249376</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ullmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma squarrulosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Bres.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8010,13 +8004,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715416</v>
+        <v>715463</v>
       </c>
       <c r="R67" t="n">
-        <v>6411386</v>
+        <v>6411631</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8045,7 +8039,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8055,7 +8049,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8064,31 +8058,30 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237010</t>
+          <t>https://artportalen.se/Sighting/137229350</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>137237025</v>
+        <v>137229355</v>
       </c>
       <c r="B68" t="n">
         <v>87556</v>
@@ -8123,10 +8116,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715360</v>
+        <v>715420</v>
       </c>
       <c r="R68" t="n">
-        <v>6411366</v>
+        <v>6411796</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8158,7 +8151,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8168,7 +8161,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8177,31 +8170,30 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237025</t>
+          <t>https://artportalen.se/Sighting/137229355</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137237028</v>
+        <v>137237004</v>
       </c>
       <c r="B69" t="n">
         <v>87556</v>
@@ -8236,10 +8228,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715269</v>
+        <v>715571</v>
       </c>
       <c r="R69" t="n">
-        <v>6411339</v>
+        <v>6411459</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8271,7 +8263,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8281,7 +8273,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8308,13 +8300,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237028</t>
+          <t>https://artportalen.se/Sighting/137237004</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>137239981</v>
+        <v>137237007</v>
       </c>
       <c r="B70" t="n">
         <v>87556</v>
@@ -8345,17 +8337,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hangvar bäcks, Gtl</t>
+          <t>Hangvar Bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715326</v>
+        <v>715435</v>
       </c>
       <c r="R70" t="n">
-        <v>6411358</v>
+        <v>6411420</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8384,7 +8376,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8394,7 +8386,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8403,30 +8395,31 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137239981</t>
+          <t>https://artportalen.se/Sighting/137237007</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>137240111</v>
+        <v>137237010</v>
       </c>
       <c r="B71" t="n">
         <v>87556</v>
@@ -8461,13 +8454,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715350</v>
+        <v>715416</v>
       </c>
       <c r="R71" t="n">
-        <v>6411745</v>
+        <v>6411386</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8496,7 +8489,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8506,7 +8499,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8522,24 +8515,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240111</t>
+          <t>https://artportalen.se/Sighting/137237010</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137240868</v>
+        <v>137237025</v>
       </c>
       <c r="B72" t="n">
         <v>87556</v>
@@ -8574,13 +8567,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715283</v>
+        <v>715360</v>
       </c>
       <c r="R72" t="n">
-        <v>6411355</v>
+        <v>6411366</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8609,7 +8602,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8619,12 +8612,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>En, tall</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8640,24 +8628,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240868</t>
+          <t>https://artportalen.se/Sighting/137237025</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137240869</v>
+        <v>137237028</v>
       </c>
       <c r="B73" t="n">
         <v>87556</v>
@@ -8692,10 +8680,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715275</v>
+        <v>715269</v>
       </c>
       <c r="R73" t="n">
-        <v>6411419</v>
+        <v>6411339</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8727,7 +8715,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8737,12 +8725,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>En, tall, mossa, gräs</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8758,24 +8741,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240869</t>
+          <t>https://artportalen.se/Sighting/137237028</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>137240870</v>
+        <v>137239981</v>
       </c>
       <c r="B74" t="n">
         <v>87556</v>
@@ -8806,17 +8789,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hangvar Bäcks, Gtl</t>
+          <t>Hangvar bäcks, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715579</v>
+        <v>715326</v>
       </c>
       <c r="R74" t="n">
-        <v>6411450</v>
+        <v>6411358</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8845,7 +8828,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8855,7 +8838,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8864,56 +8847,55 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+          <t>Bo karlstens, Martin Axegård, Pia Rydh</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240870</t>
+          <t>https://artportalen.se/Sighting/137239981</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>137240862</v>
+        <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>91534</v>
+        <v>87556</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003554</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sträv jordstjärna</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Geastrum berkeleyi</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Massee</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8923,13 +8905,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715487</v>
+        <v>715350</v>
       </c>
       <c r="R75" t="n">
-        <v>6411240</v>
+        <v>6411745</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8958,7 +8940,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8968,12 +8950,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Brakved, en, tall</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8989,27 +8966,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Pia Rydh</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240862</t>
+          <t>https://artportalen.se/Sighting/137240111</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>137237018</v>
+        <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87522</v>
+        <v>87556</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9017,21 +8994,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9041,13 +9018,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715520</v>
+        <v>715283</v>
       </c>
       <c r="R76" t="n">
-        <v>6411260</v>
+        <v>6411355</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9076,7 +9053,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9086,7 +9063,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>En, tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9095,33 +9077,34 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237018</t>
+          <t>https://artportalen.se/Sighting/137240868</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>137240116</v>
+        <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87522</v>
+        <v>87556</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9129,21 +9112,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6037417</v>
+        <v>6003295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9153,10 +9136,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715273</v>
+        <v>715275</v>
       </c>
       <c r="R77" t="n">
-        <v>6411613</v>
+        <v>6411419</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9188,7 +9171,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9198,7 +9181,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>En, tall, mossa, gräs</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9207,50 +9195,56 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240116</t>
+          <t>https://artportalen.se/Sighting/137240869</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137237022</v>
+        <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>90826</v>
+        <v>87556</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6049769</v>
+        <v>6003295</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Clitopaxillus alexandri</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gillet) G.Moreno &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9260,10 +9254,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715442</v>
+        <v>715579</v>
       </c>
       <c r="R78" t="n">
-        <v>6411226</v>
+        <v>6411450</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9295,7 +9289,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9305,7 +9299,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9321,16 +9315,692 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240870</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>137274057</v>
+      </c>
+      <c r="B79" t="n">
+        <v>87559</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>715314</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6411579</v>
+      </c>
+      <c r="S79" t="n">
+        <v>14</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137274057</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>137274061</v>
+      </c>
+      <c r="B80" t="n">
+        <v>87559</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>715333</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6411372</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137274061</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>137240862</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91534</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6003554</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Sträv jordstjärna</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Geastrum berkeleyi</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Massee</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>715487</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6411240</v>
+      </c>
+      <c r="S81" t="n">
+        <v>7</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Brakved, en, tall</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Pia Rydh</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Pia Rydh, Bo karlstens, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240862</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>137237018</v>
+      </c>
+      <c r="B82" t="n">
+        <v>87522</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>715520</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6411260</v>
+      </c>
+      <c r="S82" t="n">
+        <v>11</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237018</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>137240116</v>
+      </c>
+      <c r="B83" t="n">
+        <v>87522</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>715273</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6411613</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240116</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>137237022</v>
+      </c>
+      <c r="B84" t="n">
+        <v>90826</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6049769</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Clitopaxillus alexandri</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Gillet) G.Moreno &amp; al.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hangvar Bäcks, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>715442</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6411226</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137237022</t>
         </is>
@@ -9415,6 +10085,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137237009</v>
       </c>
       <c r="B6" t="n">
-        <v>90856</v>
+        <v>90859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137237013</v>
       </c>
       <c r="B7" t="n">
-        <v>90856</v>
+        <v>90859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137237024</v>
       </c>
       <c r="B8" t="n">
-        <v>90856</v>
+        <v>90859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137237037</v>
       </c>
       <c r="B9" t="n">
-        <v>90856</v>
+        <v>90859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137239976</v>
       </c>
       <c r="B10" t="n">
-        <v>90856</v>
+        <v>90859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>90856</v>
+        <v>90859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>87532</v>
+        <v>87535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91926</v>
+        <v>91929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87543</v>
+        <v>87546</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137229361</v>
       </c>
       <c r="B15" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137237006</v>
       </c>
       <c r="B16" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137237012</v>
       </c>
       <c r="B17" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137237032</v>
       </c>
       <c r="B18" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137237033</v>
       </c>
       <c r="B19" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137239979</v>
       </c>
       <c r="B20" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104926</v>
+        <v>104929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107809</v>
+        <v>107813</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107809</v>
+        <v>107813</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>90882</v>
+        <v>90885</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137229353</v>
       </c>
       <c r="B47" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>137237015</v>
       </c>
       <c r="B48" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>137237017</v>
       </c>
       <c r="B49" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>137237029</v>
       </c>
       <c r="B50" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>137229352</v>
       </c>
       <c r="B53" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>137237011</v>
       </c>
       <c r="B54" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237020</v>
       </c>
       <c r="B55" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237026</v>
       </c>
       <c r="B56" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237030</v>
       </c>
       <c r="B57" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137239975</v>
       </c>
       <c r="B58" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137240109</v>
       </c>
       <c r="B59" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240112</v>
       </c>
       <c r="B60" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240115</v>
       </c>
       <c r="B61" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87308</v>
+        <v>87311</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90924</v>
+        <v>90927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>137229355</v>
       </c>
       <c r="B68" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>137237004</v>
       </c>
       <c r="B69" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>137237007</v>
       </c>
       <c r="B70" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>137237010</v>
       </c>
       <c r="B71" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>137237025</v>
       </c>
       <c r="B72" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>137237028</v>
       </c>
       <c r="B73" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>137239981</v>
       </c>
       <c r="B74" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>137237018</v>
       </c>
       <c r="B82" t="n">
-        <v>87522</v>
+        <v>87525</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>137240116</v>
       </c>
       <c r="B83" t="n">
-        <v>87522</v>
+        <v>87525</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>137237022</v>
       </c>
       <c r="B84" t="n">
-        <v>90826</v>
+        <v>90829</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137274059</v>
       </c>
       <c r="B5" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137237009</v>
       </c>
       <c r="B6" t="n">
-        <v>90859</v>
+        <v>90869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137237013</v>
       </c>
       <c r="B7" t="n">
-        <v>90859</v>
+        <v>90869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137237024</v>
       </c>
       <c r="B8" t="n">
-        <v>90859</v>
+        <v>90869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137237037</v>
       </c>
       <c r="B9" t="n">
-        <v>90859</v>
+        <v>90869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137239976</v>
       </c>
       <c r="B10" t="n">
-        <v>90859</v>
+        <v>90869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>90859</v>
+        <v>90869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91929</v>
+        <v>91939</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87546</v>
+        <v>87556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137229361</v>
       </c>
       <c r="B15" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137237006</v>
       </c>
       <c r="B16" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137237012</v>
       </c>
       <c r="B17" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137237032</v>
       </c>
       <c r="B18" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137237033</v>
       </c>
       <c r="B19" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137239979</v>
       </c>
       <c r="B20" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137274058</v>
       </c>
       <c r="B22" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91602</v>
+        <v>91612</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91602</v>
+        <v>91612</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91602</v>
+        <v>91612</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91602</v>
+        <v>91612</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104929</v>
+        <v>104948</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107813</v>
+        <v>107834</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107813</v>
+        <v>107834</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>90885</v>
+        <v>90895</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137229353</v>
       </c>
       <c r="B47" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>137237015</v>
       </c>
       <c r="B48" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>137237017</v>
       </c>
       <c r="B49" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>137237029</v>
       </c>
       <c r="B50" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>137229352</v>
       </c>
       <c r="B53" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>137237011</v>
       </c>
       <c r="B54" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237020</v>
       </c>
       <c r="B55" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237026</v>
       </c>
       <c r="B56" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237030</v>
       </c>
       <c r="B57" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137239975</v>
       </c>
       <c r="B58" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137240109</v>
       </c>
       <c r="B59" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240112</v>
       </c>
       <c r="B60" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240115</v>
       </c>
       <c r="B61" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>137274060</v>
       </c>
       <c r="B64" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>137274064</v>
       </c>
       <c r="B65" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87311</v>
+        <v>87321</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90927</v>
+        <v>90937</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>137229355</v>
       </c>
       <c r="B68" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>137237004</v>
       </c>
       <c r="B69" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>137237007</v>
       </c>
       <c r="B70" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>137237010</v>
       </c>
       <c r="B71" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>137237025</v>
       </c>
       <c r="B72" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>137237028</v>
       </c>
       <c r="B73" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>137239981</v>
       </c>
       <c r="B74" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>137274057</v>
       </c>
       <c r="B79" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>137274061</v>
       </c>
       <c r="B80" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91537</v>
+        <v>91547</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>137237018</v>
       </c>
       <c r="B82" t="n">
-        <v>87525</v>
+        <v>87535</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>137240116</v>
       </c>
       <c r="B83" t="n">
-        <v>87525</v>
+        <v>87535</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>137237022</v>
       </c>
       <c r="B84" t="n">
-        <v>90829</v>
+        <v>90839</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137274059</v>
       </c>
       <c r="B5" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137237009</v>
       </c>
       <c r="B6" t="n">
-        <v>90869</v>
+        <v>90870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137237013</v>
       </c>
       <c r="B7" t="n">
-        <v>90869</v>
+        <v>90870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137237024</v>
       </c>
       <c r="B8" t="n">
-        <v>90869</v>
+        <v>90870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137237037</v>
       </c>
       <c r="B9" t="n">
-        <v>90869</v>
+        <v>90870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137239976</v>
       </c>
       <c r="B10" t="n">
-        <v>90869</v>
+        <v>90870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>90869</v>
+        <v>90870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91939</v>
+        <v>91940</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87556</v>
+        <v>87557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137229361</v>
       </c>
       <c r="B15" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137237006</v>
       </c>
       <c r="B16" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137237012</v>
       </c>
       <c r="B17" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137237032</v>
       </c>
       <c r="B18" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137237033</v>
       </c>
       <c r="B19" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137239979</v>
       </c>
       <c r="B20" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137274058</v>
       </c>
       <c r="B22" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104948</v>
+        <v>104949</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107834</v>
+        <v>107835</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>90895</v>
+        <v>90896</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137229353</v>
       </c>
       <c r="B47" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>137237015</v>
       </c>
       <c r="B48" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>137237017</v>
       </c>
       <c r="B49" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>137237029</v>
       </c>
       <c r="B50" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>137229352</v>
       </c>
       <c r="B53" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>137237011</v>
       </c>
       <c r="B54" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237020</v>
       </c>
       <c r="B55" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237026</v>
       </c>
       <c r="B56" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237030</v>
       </c>
       <c r="B57" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137239975</v>
       </c>
       <c r="B58" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137240109</v>
       </c>
       <c r="B59" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240112</v>
       </c>
       <c r="B60" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240115</v>
       </c>
       <c r="B61" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>137274060</v>
       </c>
       <c r="B64" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>137274064</v>
       </c>
       <c r="B65" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87321</v>
+        <v>87322</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90937</v>
+        <v>90938</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>137229355</v>
       </c>
       <c r="B68" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>137237004</v>
       </c>
       <c r="B69" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>137237007</v>
       </c>
       <c r="B70" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>137237010</v>
       </c>
       <c r="B71" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>137237025</v>
       </c>
       <c r="B72" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>137237028</v>
       </c>
       <c r="B73" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>137239981</v>
       </c>
       <c r="B74" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>137274057</v>
       </c>
       <c r="B79" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>137274061</v>
       </c>
       <c r="B80" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91547</v>
+        <v>91548</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>137237018</v>
       </c>
       <c r="B82" t="n">
-        <v>87535</v>
+        <v>87536</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>137240116</v>
       </c>
       <c r="B83" t="n">
-        <v>87535</v>
+        <v>87536</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>137237022</v>
       </c>
       <c r="B84" t="n">
-        <v>90839</v>
+        <v>90840</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137274059</v>
       </c>
       <c r="B5" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137237009</v>
       </c>
       <c r="B6" t="n">
-        <v>90870</v>
+        <v>90873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137237013</v>
       </c>
       <c r="B7" t="n">
-        <v>90870</v>
+        <v>90873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137237024</v>
       </c>
       <c r="B8" t="n">
-        <v>90870</v>
+        <v>90873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137237037</v>
       </c>
       <c r="B9" t="n">
-        <v>90870</v>
+        <v>90873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137239976</v>
       </c>
       <c r="B10" t="n">
-        <v>90870</v>
+        <v>90873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>90870</v>
+        <v>90873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87557</v>
+        <v>87560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137229361</v>
       </c>
       <c r="B15" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137237006</v>
       </c>
       <c r="B16" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137237012</v>
       </c>
       <c r="B17" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137237032</v>
       </c>
       <c r="B18" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137237033</v>
       </c>
       <c r="B19" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137239979</v>
       </c>
       <c r="B20" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137274058</v>
       </c>
       <c r="B22" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104949</v>
+        <v>104954</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107835</v>
+        <v>107840</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>90896</v>
+        <v>90899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137229353</v>
       </c>
       <c r="B47" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>137237015</v>
       </c>
       <c r="B48" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>137237017</v>
       </c>
       <c r="B49" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>137237029</v>
       </c>
       <c r="B50" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>137229352</v>
       </c>
       <c r="B53" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>137237011</v>
       </c>
       <c r="B54" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237020</v>
       </c>
       <c r="B55" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237026</v>
       </c>
       <c r="B56" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237030</v>
       </c>
       <c r="B57" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137239975</v>
       </c>
       <c r="B58" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137240109</v>
       </c>
       <c r="B59" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240112</v>
       </c>
       <c r="B60" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240115</v>
       </c>
       <c r="B61" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>137274060</v>
       </c>
       <c r="B64" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>137274064</v>
       </c>
       <c r="B65" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87322</v>
+        <v>87325</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90938</v>
+        <v>90941</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>137229355</v>
       </c>
       <c r="B68" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>137237004</v>
       </c>
       <c r="B69" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>137237007</v>
       </c>
       <c r="B70" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>137237010</v>
       </c>
       <c r="B71" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>137237025</v>
       </c>
       <c r="B72" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>137237028</v>
       </c>
       <c r="B73" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>137239981</v>
       </c>
       <c r="B74" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>137274057</v>
       </c>
       <c r="B79" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>137274061</v>
       </c>
       <c r="B80" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91548</v>
+        <v>91551</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>137237018</v>
       </c>
       <c r="B82" t="n">
-        <v>87536</v>
+        <v>87539</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>137240116</v>
       </c>
       <c r="B83" t="n">
-        <v>87536</v>
+        <v>87539</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>137237022</v>
       </c>
       <c r="B84" t="n">
-        <v>90840</v>
+        <v>90843</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91943</v>
+        <v>91945</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104954</v>
+        <v>104957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107840</v>
+        <v>107843</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90941</v>
+        <v>90943</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91551</v>
+        <v>91553</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137274059</v>
       </c>
       <c r="B5" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137237009</v>
       </c>
       <c r="B6" t="n">
-        <v>90873</v>
+        <v>90878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137237013</v>
       </c>
       <c r="B7" t="n">
-        <v>90873</v>
+        <v>90878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137237024</v>
       </c>
       <c r="B8" t="n">
-        <v>90873</v>
+        <v>90878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137237037</v>
       </c>
       <c r="B9" t="n">
-        <v>90873</v>
+        <v>90878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137239976</v>
       </c>
       <c r="B10" t="n">
-        <v>90873</v>
+        <v>90878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>90873</v>
+        <v>90878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91945</v>
+        <v>91950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87560</v>
+        <v>87565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137229361</v>
       </c>
       <c r="B15" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137237006</v>
       </c>
       <c r="B16" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137237012</v>
       </c>
       <c r="B17" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137237032</v>
       </c>
       <c r="B18" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137237033</v>
       </c>
       <c r="B19" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137239979</v>
       </c>
       <c r="B20" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137274058</v>
       </c>
       <c r="B22" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91618</v>
+        <v>91623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91618</v>
+        <v>91623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91618</v>
+        <v>91623</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91618</v>
+        <v>91623</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104957</v>
+        <v>104963</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107843</v>
+        <v>107849</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107843</v>
+        <v>107849</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>90899</v>
+        <v>90904</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137229353</v>
       </c>
       <c r="B47" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>137237015</v>
       </c>
       <c r="B48" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>137237017</v>
       </c>
       <c r="B49" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>137237029</v>
       </c>
       <c r="B50" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>137229352</v>
       </c>
       <c r="B53" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>137237011</v>
       </c>
       <c r="B54" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237020</v>
       </c>
       <c r="B55" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237026</v>
       </c>
       <c r="B56" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237030</v>
       </c>
       <c r="B57" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137239975</v>
       </c>
       <c r="B58" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137240109</v>
       </c>
       <c r="B59" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240112</v>
       </c>
       <c r="B60" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240115</v>
       </c>
       <c r="B61" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>137274060</v>
       </c>
       <c r="B64" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>137274064</v>
       </c>
       <c r="B65" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87325</v>
+        <v>87330</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90943</v>
+        <v>90948</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>137229355</v>
       </c>
       <c r="B68" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>137237004</v>
       </c>
       <c r="B69" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>137237007</v>
       </c>
       <c r="B70" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>137237010</v>
       </c>
       <c r="B71" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>137237025</v>
       </c>
       <c r="B72" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>137237028</v>
       </c>
       <c r="B73" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>137239981</v>
       </c>
       <c r="B74" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>137274057</v>
       </c>
       <c r="B79" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>137274061</v>
       </c>
       <c r="B80" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91553</v>
+        <v>91558</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>137237018</v>
       </c>
       <c r="B82" t="n">
-        <v>87539</v>
+        <v>87544</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>137240116</v>
       </c>
       <c r="B83" t="n">
-        <v>87539</v>
+        <v>87544</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>137237022</v>
       </c>
       <c r="B84" t="n">
-        <v>90843</v>
+        <v>90848</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104963</v>
+        <v>104964</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107849</v>
+        <v>107850</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107849</v>
+        <v>107850</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137274059</v>
       </c>
       <c r="B5" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137237009</v>
       </c>
       <c r="B6" t="n">
-        <v>90878</v>
+        <v>90889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137237013</v>
       </c>
       <c r="B7" t="n">
-        <v>90878</v>
+        <v>90889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137237024</v>
       </c>
       <c r="B8" t="n">
-        <v>90878</v>
+        <v>90889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137237037</v>
       </c>
       <c r="B9" t="n">
-        <v>90878</v>
+        <v>90889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137239976</v>
       </c>
       <c r="B10" t="n">
-        <v>90878</v>
+        <v>90889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>90878</v>
+        <v>90889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91950</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87565</v>
+        <v>87576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137229361</v>
       </c>
       <c r="B15" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137237006</v>
       </c>
       <c r="B16" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137237012</v>
       </c>
       <c r="B17" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137237032</v>
       </c>
       <c r="B18" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137237033</v>
       </c>
       <c r="B19" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137239979</v>
       </c>
       <c r="B20" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137274058</v>
       </c>
       <c r="B22" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91623</v>
+        <v>91635</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91623</v>
+        <v>91635</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91623</v>
+        <v>91635</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91623</v>
+        <v>91635</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104964</v>
+        <v>104976</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107850</v>
+        <v>107862</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>90904</v>
+        <v>90915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137229353</v>
       </c>
       <c r="B47" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>137237015</v>
       </c>
       <c r="B48" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>137237017</v>
       </c>
       <c r="B49" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>137237029</v>
       </c>
       <c r="B50" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>137229352</v>
       </c>
       <c r="B53" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>137237011</v>
       </c>
       <c r="B54" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237020</v>
       </c>
       <c r="B55" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237026</v>
       </c>
       <c r="B56" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237030</v>
       </c>
       <c r="B57" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137239975</v>
       </c>
       <c r="B58" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137240109</v>
       </c>
       <c r="B59" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240112</v>
       </c>
       <c r="B60" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240115</v>
       </c>
       <c r="B61" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>137274060</v>
       </c>
       <c r="B64" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>137274064</v>
       </c>
       <c r="B65" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87330</v>
+        <v>87341</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90948</v>
+        <v>90960</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>137229355</v>
       </c>
       <c r="B68" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>137237004</v>
       </c>
       <c r="B69" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>137237007</v>
       </c>
       <c r="B70" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>137237010</v>
       </c>
       <c r="B71" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>137237025</v>
       </c>
       <c r="B72" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>137237028</v>
       </c>
       <c r="B73" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>137239981</v>
       </c>
       <c r="B74" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>137274057</v>
       </c>
       <c r="B79" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>137274061</v>
       </c>
       <c r="B80" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91558</v>
+        <v>91570</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>137237018</v>
       </c>
       <c r="B82" t="n">
-        <v>87544</v>
+        <v>87555</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>137240116</v>
       </c>
       <c r="B83" t="n">
-        <v>87544</v>
+        <v>87555</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>137237022</v>
       </c>
       <c r="B84" t="n">
-        <v>90848</v>
+        <v>90859</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137274059</v>
       </c>
       <c r="B5" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137237009</v>
       </c>
       <c r="B6" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137237013</v>
       </c>
       <c r="B7" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137237024</v>
       </c>
       <c r="B8" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137237037</v>
       </c>
       <c r="B9" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137239976</v>
       </c>
       <c r="B10" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87576</v>
+        <v>87577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137229361</v>
       </c>
       <c r="B15" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137237006</v>
       </c>
       <c r="B16" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137237012</v>
       </c>
       <c r="B17" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137237032</v>
       </c>
       <c r="B18" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137237033</v>
       </c>
       <c r="B19" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137239979</v>
       </c>
       <c r="B20" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137274058</v>
       </c>
       <c r="B22" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91635</v>
+        <v>91636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91635</v>
+        <v>91636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91635</v>
+        <v>91636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91635</v>
+        <v>91636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104976</v>
+        <v>104977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>90915</v>
+        <v>90916</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137229353</v>
       </c>
       <c r="B47" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>137237015</v>
       </c>
       <c r="B48" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>137237017</v>
       </c>
       <c r="B49" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>137237029</v>
       </c>
       <c r="B50" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>137229352</v>
       </c>
       <c r="B53" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>137237011</v>
       </c>
       <c r="B54" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237020</v>
       </c>
       <c r="B55" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237026</v>
       </c>
       <c r="B56" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237030</v>
       </c>
       <c r="B57" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137239975</v>
       </c>
       <c r="B58" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137240109</v>
       </c>
       <c r="B59" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240112</v>
       </c>
       <c r="B60" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240115</v>
       </c>
       <c r="B61" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>137274060</v>
       </c>
       <c r="B64" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>137274064</v>
       </c>
       <c r="B65" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87341</v>
+        <v>87342</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90960</v>
+        <v>90961</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>137229355</v>
       </c>
       <c r="B68" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>137237004</v>
       </c>
       <c r="B69" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>137237007</v>
       </c>
       <c r="B70" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>137237010</v>
       </c>
       <c r="B71" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>137237025</v>
       </c>
       <c r="B72" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>137237028</v>
       </c>
       <c r="B73" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>137239981</v>
       </c>
       <c r="B74" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>137274057</v>
       </c>
       <c r="B79" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>137274061</v>
       </c>
       <c r="B80" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>137237018</v>
       </c>
       <c r="B82" t="n">
-        <v>87555</v>
+        <v>87556</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>137240116</v>
       </c>
       <c r="B83" t="n">
-        <v>87555</v>
+        <v>87556</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>137237022</v>
       </c>
       <c r="B84" t="n">
-        <v>90859</v>
+        <v>90860</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137274059</v>
       </c>
       <c r="B5" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137237009</v>
       </c>
       <c r="B6" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137237013</v>
       </c>
       <c r="B7" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137237024</v>
       </c>
       <c r="B8" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137237037</v>
       </c>
       <c r="B9" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137239976</v>
       </c>
       <c r="B10" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87577</v>
+        <v>87580</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137229361</v>
       </c>
       <c r="B15" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137237006</v>
       </c>
       <c r="B16" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137237012</v>
       </c>
       <c r="B17" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137237032</v>
       </c>
       <c r="B18" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137237033</v>
       </c>
       <c r="B19" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137239979</v>
       </c>
       <c r="B20" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137274058</v>
       </c>
       <c r="B22" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91636</v>
+        <v>91639</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91636</v>
+        <v>91639</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91636</v>
+        <v>91639</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91636</v>
+        <v>91639</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104977</v>
+        <v>104980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107863</v>
+        <v>107866</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>90916</v>
+        <v>90919</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137229353</v>
       </c>
       <c r="B47" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>137237015</v>
       </c>
       <c r="B48" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>137237017</v>
       </c>
       <c r="B49" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>137237029</v>
       </c>
       <c r="B50" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>137229352</v>
       </c>
       <c r="B53" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>137237011</v>
       </c>
       <c r="B54" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237020</v>
       </c>
       <c r="B55" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237026</v>
       </c>
       <c r="B56" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237030</v>
       </c>
       <c r="B57" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137239975</v>
       </c>
       <c r="B58" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137240109</v>
       </c>
       <c r="B59" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240112</v>
       </c>
       <c r="B60" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240115</v>
       </c>
       <c r="B61" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>137274060</v>
       </c>
       <c r="B64" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>137274064</v>
       </c>
       <c r="B65" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87342</v>
+        <v>87345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90961</v>
+        <v>90964</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>137229355</v>
       </c>
       <c r="B68" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>137237004</v>
       </c>
       <c r="B69" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>137237007</v>
       </c>
       <c r="B70" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>137237010</v>
       </c>
       <c r="B71" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>137237025</v>
       </c>
       <c r="B72" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>137237028</v>
       </c>
       <c r="B73" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>137239981</v>
       </c>
       <c r="B74" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>137274057</v>
       </c>
       <c r="B79" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>137274061</v>
       </c>
       <c r="B80" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>137237018</v>
       </c>
       <c r="B82" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>137240116</v>
       </c>
       <c r="B83" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>137237022</v>
       </c>
       <c r="B84" t="n">
-        <v>90860</v>
+        <v>90863</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 1769-2022 artfynd.xlsx
+++ b/artfynd/A 1769-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137229354</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237008</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137240108</v>
       </c>
       <c r="B4" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137274059</v>
       </c>
       <c r="B5" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>137237009</v>
       </c>
       <c r="B6" t="n">
-        <v>90893</v>
+        <v>90897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>137237013</v>
       </c>
       <c r="B7" t="n">
-        <v>90893</v>
+        <v>90897</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>137237024</v>
       </c>
       <c r="B8" t="n">
-        <v>90893</v>
+        <v>90897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137237037</v>
       </c>
       <c r="B9" t="n">
-        <v>90893</v>
+        <v>90897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>137239976</v>
       </c>
       <c r="B10" t="n">
-        <v>90893</v>
+        <v>90897</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>137240854</v>
       </c>
       <c r="B11" t="n">
-        <v>90893</v>
+        <v>90897</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>137240113</v>
       </c>
       <c r="B12" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>137240857</v>
       </c>
       <c r="B13" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>137237036</v>
       </c>
       <c r="B14" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>137229361</v>
       </c>
       <c r="B15" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>137237006</v>
       </c>
       <c r="B16" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>137237012</v>
       </c>
       <c r="B17" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>137237032</v>
       </c>
       <c r="B18" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137237033</v>
       </c>
       <c r="B19" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>137239979</v>
       </c>
       <c r="B20" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137240118</v>
       </c>
       <c r="B21" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137274058</v>
       </c>
       <c r="B22" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>137237023</v>
       </c>
       <c r="B23" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>137240861</v>
       </c>
       <c r="B24" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>137229349</v>
       </c>
       <c r="B25" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>137240114</v>
       </c>
       <c r="B26" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>137237016</v>
       </c>
       <c r="B27" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137240110</v>
       </c>
       <c r="B28" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>137237014</v>
       </c>
       <c r="B29" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>137237038</v>
       </c>
       <c r="B30" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>137239978</v>
       </c>
       <c r="B31" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>137240864</v>
       </c>
       <c r="B32" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>137237031</v>
       </c>
       <c r="B36" t="n">
-        <v>104980</v>
+        <v>104986</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>137237019</v>
       </c>
       <c r="B38" t="n">
-        <v>107866</v>
+        <v>107872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137240107</v>
       </c>
       <c r="B39" t="n">
-        <v>107866</v>
+        <v>107872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>137237021</v>
       </c>
       <c r="B46" t="n">
-        <v>90919</v>
+        <v>90923</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137229353</v>
       </c>
       <c r="B47" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>137237015</v>
       </c>
       <c r="B48" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>137237017</v>
       </c>
       <c r="B49" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>137237029</v>
       </c>
       <c r="B50" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>137239982</v>
       </c>
       <c r="B51" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>137240117</v>
       </c>
       <c r="B52" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>137229352</v>
       </c>
       <c r="B53" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>137237011</v>
       </c>
       <c r="B54" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>137237020</v>
       </c>
       <c r="B55" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>137237026</v>
       </c>
       <c r="B56" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>137237030</v>
       </c>
       <c r="B57" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>137239975</v>
       </c>
       <c r="B58" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>137240109</v>
       </c>
       <c r="B59" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>137240112</v>
       </c>
       <c r="B60" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>137240115</v>
       </c>
       <c r="B61" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>137240119</v>
       </c>
       <c r="B62" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>137240860</v>
       </c>
       <c r="B63" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>137274060</v>
       </c>
       <c r="B64" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>137274064</v>
       </c>
       <c r="B65" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>137229356</v>
       </c>
       <c r="B66" t="n">
-        <v>87345</v>
+        <v>87349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>137229350</v>
       </c>
       <c r="B67" t="n">
-        <v>90964</v>
+        <v>90968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>137229355</v>
       </c>
       <c r="B68" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>137237004</v>
       </c>
       <c r="B69" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>137237007</v>
       </c>
       <c r="B70" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>137237010</v>
       </c>
       <c r="B71" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>137237025</v>
       </c>
       <c r="B72" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>137237028</v>
       </c>
       <c r="B73" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>137239981</v>
       </c>
       <c r="B74" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>137240111</v>
       </c>
       <c r="B75" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137240868</v>
       </c>
       <c r="B76" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>137240869</v>
       </c>
       <c r="B77" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>137240870</v>
       </c>
       <c r="B78" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>137274057</v>
       </c>
       <c r="B79" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>137274061</v>
       </c>
       <c r="B80" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>137240862</v>
       </c>
       <c r="B81" t="n">
-        <v>91574</v>
+        <v>91578</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>137237018</v>
       </c>
       <c r="B82" t="n">
-        <v>87559</v>
+        <v>87563</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>137240116</v>
       </c>
       <c r="B83" t="n">
-        <v>87559</v>
+        <v>87563</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>137237022</v>
       </c>
       <c r="B84" t="n">
-        <v>90863</v>
+        <v>90867</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
